--- a/data/youtube.xlsx
+++ b/data/youtube.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D04BFCD90D7E18F8C2B3556DCAFDC78C2CC4159D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79CEDB0F-0A3B-462C-A528-30C2A3B4E56B}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_D04BFCD90D7E18F8C2B3556DCAFDC78C2CC4159D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD078590-BE52-429A-A18F-DEBCF901CBCF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="0" windowWidth="25560" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Start Date</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>VTI</t>
+  </si>
+  <si>
+    <t>Curr Weight</t>
   </si>
 </sst>
 </file>
@@ -169,6 +172,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,15 +466,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -477,8 +485,11 @@
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -489,7 +500,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -500,7 +511,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
@@ -511,7 +522,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -522,7 +533,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -533,24 +544,24 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
     </row>

--- a/data/youtube.xlsx
+++ b/data/youtube.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_D04BFCD90D7E18F8C2B3556DCAFDC78C2CC4159D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD078590-BE52-429A-A18F-DEBCF901CBCF}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_D04BFCD90D7E18F8C2B3556DCAFDC78C2CC4159D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D0E677-8C3C-46D8-814C-3722B12F44BF}"/>
   <bookViews>
     <workbookView xWindow="40" yWindow="0" windowWidth="25560" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
-    <sheet name="Dates &amp;amp; Risk Free Rate" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,16 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Risk Free Rate</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Ticker</t>
   </si>
@@ -76,23 +66,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00%"/>
+  <numFmts count="1">
     <numFmt numFmtId="165" formatCode="#,##0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -128,28 +111,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -466,145 +434,88 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B2" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B3" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
-        <v>11</v>
+      <c r="B4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B5" s="2">
         <v>0.05</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C5" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B6" s="2">
         <v>0.05</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C6" s="2">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="2" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>39231</v>
-      </c>
-      <c r="B2" s="3">
-        <v>45066</v>
-      </c>
-      <c r="C2" s="4">
-        <v>3.6999999999999998E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/youtube.xlsx
+++ b/data/youtube.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_D04BFCD90D7E18F8C2B3556DCAFDC78C2CC4159D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D0E677-8C3C-46D8-814C-3722B12F44BF}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_D04BFCD90D7E18F8C2B3556DCAFDC78C2CC4159D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8114BE-99F7-45F2-B25A-1400876E4B9B}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="0" windowWidth="25560" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0%"/>
+    <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -113,16 +113,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -140,10 +140,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -460,8 +456,8 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
+      <c r="A2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>0.05</v>
@@ -471,8 +467,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>0.05</v>
@@ -482,8 +478,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
+      <c r="A4" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="2">
         <v>0.05</v>
@@ -494,7 +490,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2">
         <v>0.05</v>
@@ -504,8 +500,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
+      <c r="A6" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>0.05</v>
